--- a/固定路线段（文本+坐标）/盐城/盐城 固定路线样式表格--1010.xlsx
+++ b/固定路线段（文本+坐标）/盐城/盐城 固定路线样式表格--1010.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\3-课题研究+琐碎\20260511 大件运输高效办成“一件事”--交通、住建、数据大件推进会\大件“最初一公里”\住建固定路线样式表\固定路线段（文本+坐标）\盐城\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E55C7E3F-0EE6-47D3-82B2-1E342FF50ACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72444F0A-F4DC-4BCA-A770-2E13B182D07E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -591,9 +591,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -602,6 +599,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1100,54 +1100,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="2" customFormat="1" ht="14" customHeight="1">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="11" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="2" customFormat="1">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
     </row>
     <row r="3" spans="1:10" ht="45">
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="7" t="s">
@@ -1179,7 +1179,7 @@
       <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B4" s="11"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="7" t="s">
         <v>5</v>
       </c>
@@ -1209,7 +1209,7 @@
       <c r="A5" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="11"/>
+      <c r="B5" s="14"/>
       <c r="C5" s="7" t="s">
         <v>14</v>
       </c>
@@ -1239,7 +1239,7 @@
       <c r="A6" s="6">
         <v>4</v>
       </c>
-      <c r="B6" s="11"/>
+      <c r="B6" s="14"/>
       <c r="C6" s="4" t="s">
         <v>6</v>
       </c>
@@ -1269,7 +1269,7 @@
       <c r="A7" s="6">
         <v>5</v>
       </c>
-      <c r="B7" s="11"/>
+      <c r="B7" s="14"/>
       <c r="C7" s="4" t="s">
         <v>17</v>
       </c>
@@ -1295,7 +1295,7 @@
       <c r="A8" s="6">
         <v>6</v>
       </c>
-      <c r="B8" s="11"/>
+      <c r="B8" s="14"/>
       <c r="C8" s="4" t="s">
         <v>24</v>
       </c>
@@ -1319,7 +1319,7 @@
       <c r="A9" s="6">
         <v>7</v>
       </c>
-      <c r="B9" s="11"/>
+      <c r="B9" s="14"/>
       <c r="C9" s="8" t="s">
         <v>25</v>
       </c>
@@ -1343,7 +1343,7 @@
       <c r="A10" s="6">
         <v>8</v>
       </c>
-      <c r="B10" s="11"/>
+      <c r="B10" s="14"/>
       <c r="C10" s="4" t="s">
         <v>28</v>
       </c>
@@ -1367,7 +1367,7 @@
       <c r="A11" s="6">
         <v>9</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="14" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="4" t="s">
@@ -1395,7 +1395,7 @@
       <c r="A12" s="6">
         <v>10</v>
       </c>
-      <c r="B12" s="11"/>
+      <c r="B12" s="14"/>
       <c r="C12" s="4" t="s">
         <v>36</v>
       </c>
@@ -1421,7 +1421,7 @@
       <c r="A13" s="6">
         <v>11</v>
       </c>
-      <c r="B13" s="11"/>
+      <c r="B13" s="14"/>
       <c r="C13" s="4" t="s">
         <v>31</v>
       </c>
@@ -1447,7 +1447,7 @@
       <c r="A14" s="6">
         <v>12</v>
       </c>
-      <c r="B14" s="11"/>
+      <c r="B14" s="14"/>
       <c r="C14" s="4" t="s">
         <v>36</v>
       </c>
@@ -1473,7 +1473,7 @@
       <c r="A15" s="6">
         <v>13</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="14" t="s">
         <v>49</v>
       </c>
       <c r="C15" s="4" t="s">
@@ -1501,7 +1501,7 @@
       <c r="A16" s="6">
         <v>14</v>
       </c>
-      <c r="B16" s="11"/>
+      <c r="B16" s="14"/>
       <c r="C16" s="4" t="s">
         <v>47</v>
       </c>
@@ -1527,7 +1527,7 @@
       <c r="A17" s="6">
         <v>15</v>
       </c>
-      <c r="B17" s="11"/>
+      <c r="B17" s="14"/>
       <c r="C17" s="4" t="s">
         <v>50</v>
       </c>
@@ -1553,7 +1553,7 @@
       <c r="A18" s="6">
         <v>16</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="14" t="s">
         <v>52</v>
       </c>
       <c r="C18" s="4" t="s">
@@ -1581,7 +1581,7 @@
       <c r="A19" s="6">
         <v>17</v>
       </c>
-      <c r="B19" s="11"/>
+      <c r="B19" s="14"/>
       <c r="C19" s="4" t="s">
         <v>89</v>
       </c>
@@ -1607,7 +1607,7 @@
       <c r="A20" s="6">
         <v>18</v>
       </c>
-      <c r="B20" s="11"/>
+      <c r="B20" s="14"/>
       <c r="C20" s="4" t="s">
         <v>59</v>
       </c>
@@ -1635,7 +1635,7 @@
       <c r="A21" s="6">
         <v>19</v>
       </c>
-      <c r="B21" s="11"/>
+      <c r="B21" s="14"/>
       <c r="C21" s="4" t="s">
         <v>63</v>
       </c>
@@ -1663,7 +1663,7 @@
       <c r="A22" s="6">
         <v>20</v>
       </c>
-      <c r="B22" s="11"/>
+      <c r="B22" s="14"/>
       <c r="C22" s="4" t="s">
         <v>65</v>
       </c>
@@ -1689,7 +1689,7 @@
       <c r="A23" s="6">
         <v>21</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="14" t="s">
         <v>67</v>
       </c>
       <c r="C23" s="4" t="s">
@@ -1719,7 +1719,7 @@
       <c r="A24" s="6">
         <v>22</v>
       </c>
-      <c r="B24" s="11"/>
+      <c r="B24" s="14"/>
       <c r="C24" s="4" t="s">
         <v>103</v>
       </c>
@@ -1747,7 +1747,7 @@
       <c r="A25" s="6">
         <v>23</v>
       </c>
-      <c r="B25" s="11"/>
+      <c r="B25" s="14"/>
       <c r="C25" s="4" t="s">
         <v>76</v>
       </c>
@@ -1775,7 +1775,7 @@
       <c r="A26" s="6">
         <v>24</v>
       </c>
-      <c r="B26" s="11"/>
+      <c r="B26" s="14"/>
       <c r="C26" s="4" t="s">
         <v>80</v>
       </c>
@@ -1831,6 +1831,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B3:B10"/>
+    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B18:B22"/>
+    <mergeCell ref="B23:B26"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="H1:H2"/>
@@ -1841,11 +1846,6 @@
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="B3:B10"/>
-    <mergeCell ref="B11:B14"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B18:B22"/>
-    <mergeCell ref="B23:B26"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.156944444444444" right="7.8472222222222193E-2" top="0.23611111111111099" bottom="0.23611111111111099" header="0.196527777777778" footer="0.156944444444444"/>
